--- a/data/trending_integrated_20260915_12.xlsx
+++ b/data/trending_integrated_20260915_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10770</v>
+        <v>10870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.18%</t>
+          <t>'+17.26%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H2" t="n">
         <v>1.19</v>
@@ -610,7 +610,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>133228096275</v>
+        <v>134471614375</v>
       </c>
       <c r="P2" t="n">
         <v>25050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>면역조절 펩타이드 신기술 특허 등록. 장기지속형 제제 기술 기반 상승 기대.</t>
+          <t>면역 조절 펩타이드 기술 특허 등록 및 기대감. 유통 물량 적은 품절주.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신기술', '특허등록', '면역조절']</t>
+          <t>['특허', '품절주', '펩타이드']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25200</v>
+        <v>2995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.07%</t>
+          <t>'+15.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.01</v>
+        <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
         <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>1.34</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>21900</v>
+        <v>2585</v>
       </c>
       <c r="K3" t="n">
-        <v>21700</v>
+        <v>2725</v>
       </c>
       <c r="L3" t="n">
-        <v>26750</v>
+        <v>3200</v>
       </c>
       <c r="M3" t="n">
-        <v>21500</v>
+        <v>2690</v>
       </c>
       <c r="N3" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>180097812950</v>
+        <v>71050964334</v>
       </c>
       <c r="P3" t="n">
-        <v>50600</v>
+        <v>5100</v>
       </c>
       <c r="Q3" t="n">
-        <v>10380</v>
+        <v>966</v>
       </c>
       <c r="R3" t="n">
-        <v>-76000</v>
+        <v>-461000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>프로그램 매물 감소와 정배열 기대감 속에서 주가 상승 흐름이 좋으나, 뚜렷한 공시나 뉴스는 부재함.</t>
+          <t>미국 기업과 594억 공급 계약 및 세계 최초 타이틀. 트럼프 AI 발언에 따른 기대감 상승.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정배열', '프로그램 매물', '공시']</t>
+          <t>['공급 계약', 'AI', '세계 최초']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2925</v>
+        <v>25200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.15%</t>
+          <t>'+15.07%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.34</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H4" t="n">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2585</v>
+        <v>21900</v>
       </c>
       <c r="K4" t="n">
-        <v>2725</v>
+        <v>21700</v>
       </c>
       <c r="L4" t="n">
-        <v>3200</v>
+        <v>26750</v>
       </c>
       <c r="M4" t="n">
-        <v>2690</v>
+        <v>21500</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O4" t="n">
-        <v>66068141421</v>
+        <v>183380277300</v>
       </c>
       <c r="P4" t="n">
-        <v>5100</v>
+        <v>50600</v>
       </c>
       <c r="Q4" t="n">
-        <v>966</v>
+        <v>10380</v>
       </c>
       <c r="R4" t="n">
-        <v>-461000</v>
+        <v>-76000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 기업과 594억 공급 계약 및 세계 최초 타이틀. 트럼프 AI 발언에 따른 기대감 상승.</t>
+          <t>프로그램 매물 감소와 정배열 기대감 속에서 주가 상승 흐름이 좋으나, 뚜렷한 공시나 뉴스는 부재함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공급 계약', 'AI', '세계 최초']</t>
+          <t>['정배열', '프로그램 매물', '공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35400</v>
+        <v>51600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.27%</t>
+          <t>'+7.95%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>255</v>
+        <v>416</v>
       </c>
       <c r="H5" t="n">
-        <v>14.93</v>
+        <v>13.97</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>33000</v>
+        <v>47800</v>
       </c>
       <c r="K5" t="n">
-        <v>32750</v>
+        <v>47300</v>
       </c>
       <c r="L5" t="n">
-        <v>37200</v>
+        <v>54600</v>
       </c>
       <c r="M5" t="n">
-        <v>32750</v>
+        <v>46400</v>
       </c>
       <c r="N5" t="n">
-        <v>15.06</v>
+        <v>14.15</v>
       </c>
       <c r="O5" t="n">
-        <v>43326004225</v>
+        <v>75478393975</v>
       </c>
       <c r="P5" t="n">
-        <v>50400</v>
+        <v>108900</v>
       </c>
       <c r="Q5" t="n">
-        <v>23650</v>
+        <v>18230</v>
       </c>
       <c r="R5" t="n">
-        <v>318000</v>
+        <v>89000</v>
       </c>
       <c r="S5" t="n">
-        <v>73000</v>
+        <v>21000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
+          <t>대규모 수주 공시 기반 성장 전망. 연기금 등 기관 투자자 매수세 유입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저PBR', '현대제철', '상승']</t>
+          <t>['수주', '공시', '성장']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,82 +919,82 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3645</v>
+        <v>35400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.21%</t>
+          <t>'+7.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>177</v>
+        <v>268</v>
       </c>
       <c r="H6" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3400</v>
+        <v>33000</v>
       </c>
       <c r="K6" t="n">
-        <v>3450</v>
+        <v>32750</v>
       </c>
       <c r="L6" t="n">
-        <v>4080</v>
+        <v>37200</v>
       </c>
       <c r="M6" t="n">
-        <v>3445</v>
+        <v>32750</v>
       </c>
       <c r="N6" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O6" t="n">
-        <v>140071500806</v>
+        <v>43601821325</v>
       </c>
       <c r="P6" t="n">
-        <v>4335</v>
+        <v>50400</v>
       </c>
       <c r="Q6" t="n">
-        <v>1246</v>
+        <v>23650</v>
       </c>
       <c r="R6" t="n">
-        <v>226000</v>
+        <v>318000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼익제약과의 경쟁 구도 속에서 주가 변동성. 단기 트레이딩 관점 및 3700원 돌파 여부 주목.</t>
+          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['단타', '삼익제약', '3700원']</t>
+          <t>['저PBR', '현대제철', '상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,99 +1016,99 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51100</v>
+        <v>3635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.90%</t>
+          <t>'+6.91%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.18</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>390</v>
+        <v>178</v>
       </c>
       <c r="H7" t="n">
-        <v>13.97</v>
+        <v>0.83</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>47800</v>
+        <v>3400</v>
       </c>
       <c r="K7" t="n">
-        <v>47300</v>
+        <v>3450</v>
       </c>
       <c r="L7" t="n">
-        <v>54600</v>
+        <v>4080</v>
       </c>
       <c r="M7" t="n">
-        <v>46400</v>
+        <v>3445</v>
       </c>
       <c r="N7" t="n">
-        <v>14.15</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>74420965275</v>
+        <v>140529254553</v>
       </c>
       <c r="P7" t="n">
-        <v>108900</v>
+        <v>4335</v>
       </c>
       <c r="Q7" t="n">
-        <v>18230</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>89000</v>
+        <v>226000</v>
       </c>
       <c r="S7" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>5천억 수주 공시 후 주가 급등. 미국 진출 본격화 및 수소법 시행 기대감.</t>
+          <t>삼익제약과의 경쟁 구도 속에서 주가 변동성. 단기 트레이딩 관점 및 3700원 돌파 여부 주목.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주공시', '미국진출', '수소법']</t>
+          <t>['단타', '삼익제약', '3700원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14950</v>
+        <v>14900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.95%</t>
+          <t>'+5.60%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H8" t="n">
         <v>10.75</v>
@@ -1162,7 +1162,7 @@
         <v>10.69</v>
       </c>
       <c r="O8" t="n">
-        <v>104294656560</v>
+        <v>105234904390</v>
       </c>
       <c r="P8" t="n">
         <v>23550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31800</v>
+        <v>31900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.78%</t>
+          <t>'+5.11%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>655</v>
+        <v>705</v>
       </c>
       <c r="H9" t="n">
         <v>17.5</v>
@@ -1254,7 +1254,7 @@
         <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>10926243650</v>
+        <v>11054945950</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 기대감 속 담관암 신약 관련 소식 혼재. 기관 외인 동향 주시.</t>
+          <t>신약 FDA 승인 기대감 속 불확실성 존재. 제약 유증 및 주가 급락 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HLB', 'FDA', '담관암']</t>
+          <t>['신약', 'FDA', '유증']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141700</v>
+        <v>141900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.66%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H10" t="n">
         <v>15.81</v>
@@ -1346,7 +1346,7 @@
         <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>91644698550</v>
+        <v>92665176450</v>
       </c>
       <c r="P10" t="n">
         <v>164700</v>
@@ -1406,13 +1406,13 @@
         <v>-2.35</v>
       </c>
       <c r="E11" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G11" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H11" t="n">
         <v>0.35</v>
@@ -1438,7 +1438,7 @@
         <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>154212525410</v>
+        <v>156247950750</v>
       </c>
       <c r="P11" t="n">
         <v>30550</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 양자 보안주와 함께 상승 기대. 세계 최초 기술력 기반 신고가 돌파.</t>
+          <t>미국 양자 보안주 강세 속 관련 테마 기대. 단기 과열 및 변동성 주의.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['양자보안', '신고가', '세계최초']</t>
+          <t>['양자보안', '테마', '변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10560</v>
+        <v>10550</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G12" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H12" t="n">
         <v>17.93</v>
@@ -1530,7 +1530,7 @@
         <v>17.67</v>
       </c>
       <c r="O12" t="n">
-        <v>314642764530</v>
+        <v>316206812135</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 및 트럼프 관련 언급으로 인한 기대감 상승. 미국 시장 흐름 및 기타법인 매수세 확인.</t>
+          <t>아이온큐 급등 및 트럼프 AI 정책 강화 속 광통신 테마 기대감. 기타법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '트럼프', '기타법인']</t>
+          <t>['광통신', 'AI', '아이온큐']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19130</v>
+        <v>19190</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="H13" t="n">
         <v>10.53</v>
@@ -1622,7 +1622,7 @@
         <v>10.55</v>
       </c>
       <c r="O13" t="n">
-        <v>47653229890</v>
+        <v>48778588495</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1667,215 +1667,215 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1724000</v>
+        <v>7040</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.59%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.2</v>
+        <v>-0.97</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>472</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>2126</v>
+        <v>110</v>
       </c>
       <c r="H14" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1697000</v>
+        <v>6900</v>
       </c>
       <c r="K14" t="n">
-        <v>1690000</v>
+        <v>7500</v>
       </c>
       <c r="L14" t="n">
-        <v>1729000</v>
+        <v>8190</v>
       </c>
       <c r="M14" t="n">
-        <v>1685000</v>
+        <v>6730</v>
       </c>
       <c r="N14" t="n">
-        <v>50.47</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>2366805191500</v>
+        <v>32932735150</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q14" t="n">
-        <v>325000</v>
+        <v>2965</v>
       </c>
       <c r="R14" t="n">
-        <v>-118000</v>
+        <v>61000</v>
       </c>
       <c r="S14" t="n">
-        <v>-48000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>나스닥 선물 및 코스피 야간 선물 흐름 긍정적. 외인 매도세 속 기관 매수세 유입.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['나스닥', 'AI', '외인매도']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7000</v>
+        <v>1718000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.45%</t>
+          <t>'+1.24%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.97</v>
+        <v>-0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>473</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>2112</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7</v>
+        <v>50.27</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6900</v>
+        <v>1697000</v>
       </c>
       <c r="K15" t="n">
-        <v>7500</v>
+        <v>1690000</v>
       </c>
       <c r="L15" t="n">
-        <v>8190</v>
+        <v>1729000</v>
       </c>
       <c r="M15" t="n">
-        <v>6730</v>
+        <v>1685000</v>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>50.47</v>
       </c>
       <c r="O15" t="n">
-        <v>32193808505</v>
+        <v>2425452655500</v>
       </c>
       <c r="P15" t="n">
-        <v>10360</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>2965</v>
+        <v>325000</v>
       </c>
       <c r="R15" t="n">
-        <v>61000</v>
+        <v>-118000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>-48000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>AI 관련 긍정적 전망 속 기관 매수세 유입. 금리 인상 및 시장 변동성 주의.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['AI', '기관', '시장']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>251500</v>
+        <v>10070</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.00%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>86</v>
       </c>
       <c r="F16" t="n">
-        <v>486</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>1706</v>
+        <v>94</v>
       </c>
       <c r="H16" t="n">
-        <v>46.57</v>
+        <v>0.6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>249000</v>
+        <v>9990</v>
       </c>
       <c r="K16" t="n">
-        <v>248000</v>
+        <v>10110</v>
       </c>
       <c r="L16" t="n">
-        <v>252000</v>
+        <v>11390</v>
       </c>
       <c r="M16" t="n">
-        <v>247500</v>
+        <v>9980</v>
       </c>
       <c r="N16" t="n">
-        <v>46.64</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1265343172500</v>
+        <v>146800373925</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q16" t="n">
-        <v>75900</v>
+        <v>3500</v>
       </c>
       <c r="R16" t="n">
-        <v>-176000</v>
+        <v>21000</v>
       </c>
       <c r="S16" t="n">
-        <v>-267000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>시장 안정화 및 메모리 반도체 수요 유지 기대감. 악재 선반영 후 급반등 전망.</t>
+          <t>주가 조작 및 공매도 관련 부정적 언급 다수. 신약 관련 기대감 있으나 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['메모리반도체', '악재선반영', '급반등']</t>
+          <t>['주가조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10080</v>
+        <v>250750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.90%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>486</v>
       </c>
       <c r="G17" t="n">
-        <v>95</v>
+        <v>1706</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6</v>
+        <v>46.57</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9990</v>
+        <v>249000</v>
       </c>
       <c r="K17" t="n">
-        <v>10110</v>
+        <v>248000</v>
       </c>
       <c r="L17" t="n">
-        <v>11390</v>
+        <v>252000</v>
       </c>
       <c r="M17" t="n">
-        <v>9980</v>
+        <v>247500</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6</v>
+        <v>46.64</v>
       </c>
       <c r="O17" t="n">
-        <v>146525045665</v>
+        <v>1311345993500</v>
       </c>
       <c r="P17" t="n">
-        <v>15960</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>3500</v>
+        <v>75900</v>
       </c>
       <c r="R17" t="n">
-        <v>21000</v>
+        <v>-176000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-267000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 부정적 언급 다수. 신약 관련 기대감 있으나 구체적 근거 부족.</t>
+          <t>시장 안정화 기대감 속 저가 매수 기회 언급. 일부 악재 선반영 및 반등 가능성 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '신약']</t>
+          <t>['시장', '반등', '저가매수']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>226500</v>
+        <v>14730</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.15</v>
+        <v>-1.17</v>
       </c>
       <c r="E18" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F18" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G18" t="n">
-        <v>748</v>
+        <v>314</v>
       </c>
       <c r="H18" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>225000</v>
+        <v>14660</v>
       </c>
       <c r="K18" t="n">
-        <v>228500</v>
+        <v>14980</v>
       </c>
       <c r="L18" t="n">
-        <v>229000</v>
+        <v>15460</v>
       </c>
       <c r="M18" t="n">
-        <v>219500</v>
+        <v>14330</v>
       </c>
       <c r="N18" t="n">
-        <v>7.05</v>
+        <v>1.17</v>
       </c>
       <c r="O18" t="n">
-        <v>71015994500</v>
+        <v>39843514150</v>
       </c>
       <c r="P18" t="n">
-        <v>426000</v>
+        <v>36200</v>
       </c>
       <c r="Q18" t="n">
-        <v>89500</v>
+        <v>8920</v>
       </c>
       <c r="R18" t="n">
-        <v>-110000</v>
+        <v>-7000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>테슬라 테라팹 공급 계약 체결. AI 반도체 시장 성장 및 주주 환원 기대.</t>
+          <t>국제 유가 상승에도 주가 약보합세. 이란 관련 지정학적 리스크 및 수급 불안정.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['테슬라', '테라팹', 'AI반도체']</t>
+          <t>['국제유가', '지정학적리스크', '수급불안정']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14670</v>
+        <v>226000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.17</v>
+        <v>0.15</v>
       </c>
       <c r="E19" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
-        <v>310</v>
+        <v>759</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14660</v>
+        <v>225000</v>
       </c>
       <c r="K19" t="n">
-        <v>14980</v>
+        <v>228500</v>
       </c>
       <c r="L19" t="n">
-        <v>15460</v>
+        <v>229000</v>
       </c>
       <c r="M19" t="n">
-        <v>14330</v>
+        <v>219500</v>
       </c>
       <c r="N19" t="n">
-        <v>1.17</v>
+        <v>7.05</v>
       </c>
       <c r="O19" t="n">
-        <v>39508665210</v>
+        <v>71262225000</v>
       </c>
       <c r="P19" t="n">
-        <v>36200</v>
+        <v>426000</v>
       </c>
       <c r="Q19" t="n">
-        <v>8920</v>
+        <v>89500</v>
       </c>
       <c r="R19" t="n">
-        <v>-7000</v>
+        <v>-110000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>국제 유가 상승에도 주가 약보합세. 이란 관련 지정학적 리스크 및 수급 불안정.</t>
+          <t>테슬라 테라팹 공급 계약 체결. AI 반도체 시장 성장 및 주주 환원 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적리스크', '수급불안정']</t>
+          <t>['테슬라', '테라팹', 'AI반도체']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14400</v>
+        <v>14390</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.62%</t>
+          <t>'-0.69%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="H20" t="n">
         <v>1.8</v>
@@ -2266,7 +2266,7 @@
         <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>47873123050</v>
+        <v>48752084765</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>대한광통신, 미디어 노출 및 기술적 지지선 언급. 금리, 유가 등 매크로 변수 영향.</t>
+          <t>광통신 관련주 동반 상승 속 주가 키 맞추기 기대. 외국인 보유율 안정적.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['대한광통신', '광통신', '미증시']</t>
+          <t>['광통신', '키맞추기', '외국인']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8770</v>
+        <v>86200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.90%</t>
+          <t>'-0.92%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="G21" t="n">
-        <v>323</v>
+        <v>711</v>
       </c>
       <c r="H21" t="n">
-        <v>27.16</v>
+        <v>23.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8850</v>
+        <v>87000</v>
       </c>
       <c r="K21" t="n">
-        <v>8750</v>
+        <v>86200</v>
       </c>
       <c r="L21" t="n">
-        <v>8840</v>
+        <v>86800</v>
       </c>
       <c r="M21" t="n">
-        <v>8670</v>
+        <v>85000</v>
       </c>
       <c r="N21" t="n">
-        <v>27.16</v>
+        <v>23.56</v>
       </c>
       <c r="O21" t="n">
-        <v>15673511645</v>
+        <v>88374096900</v>
       </c>
       <c r="P21" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>8120</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-290000</v>
+        <v>-169000</v>
       </c>
       <c r="S21" t="n">
-        <v>-1000</v>
+        <v>-55000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>하반기 실적 부진 및 대표이사 사퇴 요구. 저평가 논란 속 목표 주가 하향 조정.</t>
+          <t>원전 사업 확대 기대감 속 긍정적 전망. 유가 상승 및 에너지 독립 필요성 부각.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['실적부진', '저평가', '목표주가']</t>
+          <t>['원전', '에너지', '유가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86200</v>
+        <v>8760</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="F22" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>697</v>
+        <v>328</v>
       </c>
       <c r="H22" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K22" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L22" t="n">
-        <v>86800</v>
+        <v>8840</v>
       </c>
       <c r="M22" t="n">
-        <v>85000</v>
+        <v>8670</v>
       </c>
       <c r="N22" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O22" t="n">
-        <v>87574309800</v>
+        <v>15901830565</v>
       </c>
       <c r="P22" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q22" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R22" t="n">
-        <v>-169000</v>
+        <v>-290000</v>
       </c>
       <c r="S22" t="n">
-        <v>-55000</v>
+        <v>-1000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 원전 사업 기대감 및 타 에너지 종목 강세와 함께 주가 반등 모색. 단기 변동성 존재.</t>
+          <t>경영진 교체 요구 및 실적 부진 지속. 목표주가 하향 조정 및 저평가 논란.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['두산에너빌리티', '원전', '에너지']</t>
+          <t>['실적', '목표주가', '경영진']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4195</v>
+        <v>4180</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.01%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.18</v>
       </c>
       <c r="E23" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H23" t="n">
         <v>0.77</v>
@@ -2542,7 +2542,7 @@
         <v>0.59</v>
       </c>
       <c r="O23" t="n">
-        <v>62645746908</v>
+        <v>63241928581</v>
       </c>
       <c r="P23" t="n">
         <v>8100</v>
@@ -2602,13 +2602,13 @@
         <v>0.09</v>
       </c>
       <c r="E24" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F24" t="n">
         <v>79</v>
       </c>
       <c r="G24" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H24" t="n">
         <v>28.9</v>
@@ -2634,7 +2634,7 @@
         <v>28.81</v>
       </c>
       <c r="O24" t="n">
-        <v>48137972975</v>
+        <v>49266479275</v>
       </c>
       <c r="P24" t="n">
         <v>35350</v>

--- a/data/trending_integrated_20260915_12.xlsx
+++ b/data/trending_integrated_20260915_12.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10870</v>
+        <v>3000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.26%</t>
+          <t>'+16.05%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.06</v>
+        <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="H2" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,91 +595,91 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9270</v>
+        <v>2585</v>
       </c>
       <c r="K2" t="n">
-        <v>9810</v>
+        <v>2725</v>
       </c>
       <c r="L2" t="n">
-        <v>12050</v>
+        <v>3200</v>
       </c>
       <c r="M2" t="n">
-        <v>9800</v>
+        <v>2690</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>134471614375</v>
+        <v>73557376240</v>
       </c>
       <c r="P2" t="n">
-        <v>25050</v>
+        <v>5100</v>
       </c>
       <c r="Q2" t="n">
-        <v>3705</v>
+        <v>966</v>
       </c>
       <c r="R2" t="n">
-        <v>16000</v>
+        <v>-461000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>면역 조절 펩타이드 기술 특허 등록 및 기대감. 유통 물량 적은 품절주.</t>
+          <t>미국 기업과 594억 공급 계약 및 세계 최초 타이틀. 트럼프 AI 발언에 따른 기대감 상승.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['특허', '품절주', '펩타이드']</t>
+          <t>['공급 계약', 'AI', '세계 최초']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2995</v>
+        <v>10680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.86%</t>
+          <t>'+15.21%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.34</v>
+        <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,60 +687,60 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2585</v>
+        <v>9270</v>
       </c>
       <c r="K3" t="n">
-        <v>2725</v>
+        <v>9810</v>
       </c>
       <c r="L3" t="n">
-        <v>3200</v>
+        <v>12050</v>
       </c>
       <c r="M3" t="n">
-        <v>2690</v>
+        <v>9800</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>71050964334</v>
+        <v>136043486895</v>
       </c>
       <c r="P3" t="n">
-        <v>5100</v>
+        <v>25050</v>
       </c>
       <c r="Q3" t="n">
-        <v>966</v>
+        <v>3705</v>
       </c>
       <c r="R3" t="n">
-        <v>-461000</v>
+        <v>16000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 기업과 594억 공급 계약 및 세계 최초 타이틀. 트럼프 AI 발언에 따른 기대감 상승.</t>
+          <t>품절주 특성 및 장기지속형 주사제 관련 기대감으로 인한 강한 상승세.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공급 계약', 'AI', '세계 최초']</t>
+          <t>['품절주', '장기지속형 주사제', '상승세']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25200</v>
+        <v>25000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.07%</t>
+          <t>'+14.16%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -794,7 +794,7 @@
         <v>4.89</v>
       </c>
       <c r="O4" t="n">
-        <v>183380277300</v>
+        <v>187306207875</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51600</v>
+        <v>51200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.95%</t>
+          <t>'+7.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.18</v>
       </c>
       <c r="E5" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F5" t="n">
         <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="H5" t="n">
         <v>13.97</v>
@@ -886,7 +886,7 @@
         <v>14.15</v>
       </c>
       <c r="O5" t="n">
-        <v>75478393975</v>
+        <v>76108666075</v>
       </c>
       <c r="P5" t="n">
         <v>108900</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대규모 수주 공시 기반 성장 전망. 연기금 등 기관 투자자 매수세 유입.</t>
+          <t>연이은 대형 수주 공시 기반으로 한 긍정적 전망. 수소법 시행 및 시장 확대 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['수주', '공시', '성장']</t>
+          <t>['수주 공시', '수소법', '대형 계약']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35400</v>
+        <v>35250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.27%</t>
+          <t>'+6.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H6" t="n">
         <v>14.93</v>
@@ -978,7 +978,7 @@
         <v>15.06</v>
       </c>
       <c r="O6" t="n">
-        <v>43601821325</v>
+        <v>43885139825</v>
       </c>
       <c r="P6" t="n">
         <v>50400</v>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3635</v>
+        <v>3620</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.91%</t>
+          <t>'+6.47%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
         <v>178</v>
@@ -1070,7 +1070,7 @@
         <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>140529254553</v>
+        <v>141088224242</v>
       </c>
       <c r="P7" t="n">
         <v>4335</v>
@@ -1115,79 +1115,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14900</v>
+        <v>31950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.60%</t>
+          <t>'+5.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="G8" t="n">
-        <v>161</v>
+        <v>765</v>
       </c>
       <c r="H8" t="n">
-        <v>10.75</v>
+        <v>17.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14110</v>
+        <v>30350</v>
       </c>
       <c r="K8" t="n">
-        <v>14110</v>
+        <v>30250</v>
       </c>
       <c r="L8" t="n">
-        <v>15250</v>
+        <v>32300</v>
       </c>
       <c r="M8" t="n">
-        <v>13400</v>
+        <v>30250</v>
       </c>
       <c r="N8" t="n">
-        <v>10.69</v>
+        <v>17.55</v>
       </c>
       <c r="O8" t="n">
-        <v>105234904390</v>
+        <v>11288019275</v>
       </c>
       <c r="P8" t="n">
-        <v>23550</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>5700</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-68000</v>
+        <v>25000</v>
       </c>
       <c r="S8" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>담관암 FDA 승인 관련 기대감과 동시에 실패 가능성 및 유증 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['담관암', 'FDA 승인', '유증']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,91 +1195,91 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31900</v>
+        <v>14830</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.11%</t>
+          <t>'+5.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>705</v>
+        <v>162</v>
       </c>
       <c r="H9" t="n">
-        <v>17.5</v>
+        <v>10.75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>30350</v>
+        <v>14110</v>
       </c>
       <c r="K9" t="n">
-        <v>30250</v>
+        <v>14110</v>
       </c>
       <c r="L9" t="n">
-        <v>32300</v>
+        <v>15250</v>
       </c>
       <c r="M9" t="n">
-        <v>30250</v>
+        <v>13400</v>
       </c>
       <c r="N9" t="n">
-        <v>17.55</v>
+        <v>10.69</v>
       </c>
       <c r="O9" t="n">
-        <v>11054945950</v>
+        <v>106838262475</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>23550</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>5700</v>
       </c>
       <c r="R9" t="n">
-        <v>25000</v>
+        <v>-68000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신약 FDA 승인 기대감 속 불확실성 존재. 제약 유증 및 주가 급락 우려.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['신약', 'FDA', '유증']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141900</v>
+        <v>142000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+3.88%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H10" t="n">
         <v>15.81</v>
@@ -1346,7 +1346,7 @@
         <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>92665176450</v>
+        <v>93580324050</v>
       </c>
       <c r="P10" t="n">
         <v>164700</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>합병 반대 의견이 다수 제기되었으나, 구체적인 근거나 합병 철회 가능성에 대한 객관적인 정보 부족. 주가 하락에 대한 부정적인 전망이 지배적임.</t>
+          <t>합병 반대 주장과 함께 주가 하락 및 폭락에 대한 우려가 제기됨. 일부 긍정적 요인 언급에도 불구하고 부정적 전망이 우세함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['합병', '반대', '적자']</t>
+          <t>['합병', '정정신고서', '폭락']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17700</v>
+        <v>7140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.91%</t>
+          <t>'+3.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-2.35</v>
+        <v>-0.97</v>
       </c>
       <c r="E11" t="n">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="H11" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,60 +1423,60 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17200</v>
+        <v>6900</v>
       </c>
       <c r="K11" t="n">
-        <v>17220</v>
+        <v>7500</v>
       </c>
       <c r="L11" t="n">
-        <v>18390</v>
+        <v>8190</v>
       </c>
       <c r="M11" t="n">
-        <v>16600</v>
+        <v>6730</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>156247950750</v>
+        <v>37226223145</v>
       </c>
       <c r="P11" t="n">
-        <v>30550</v>
+        <v>10360</v>
       </c>
       <c r="Q11" t="n">
-        <v>6100</v>
+        <v>2965</v>
       </c>
       <c r="R11" t="n">
-        <v>149000</v>
+        <v>61000</v>
       </c>
       <c r="S11" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 강세 속 관련 테마 기대. 단기 과열 및 변동성 주의.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['양자보안', '테마', '변동성']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10550</v>
+        <v>10540</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.63%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="H12" t="n">
         <v>17.93</v>
@@ -1530,7 +1530,7 @@
         <v>17.67</v>
       </c>
       <c r="O12" t="n">
-        <v>316206812135</v>
+        <v>318860712795</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>아이온큐 급등 및 트럼프 AI 정책 강화 속 광통신 테마 기대감. 기타법인 매수세 유입.</t>
+          <t>AI 발전 기대감 및 아이온큐 급등에 따른 긍정적 전망. 그러나 객관적 근거 부족.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '아이온큐']</t>
+          <t>['AI', '아이온큐', '광통신']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19190</v>
+        <v>19220</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.29%</t>
+          <t>'+2.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="H13" t="n">
         <v>10.53</v>
@@ -1613,7 +1613,7 @@
         <v>18440</v>
       </c>
       <c r="L13" t="n">
-        <v>19245</v>
+        <v>19330</v>
       </c>
       <c r="M13" t="n">
         <v>18120</v>
@@ -1622,7 +1622,7 @@
         <v>10.55</v>
       </c>
       <c r="O13" t="n">
-        <v>48778588495</v>
+        <v>51295027705</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7040</v>
+        <v>17530</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+1.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.97</v>
+        <v>-2.35</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G14" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6900</v>
+        <v>17200</v>
       </c>
       <c r="K14" t="n">
-        <v>7500</v>
+        <v>17220</v>
       </c>
       <c r="L14" t="n">
-        <v>8190</v>
+        <v>18390</v>
       </c>
       <c r="M14" t="n">
-        <v>6730</v>
+        <v>16600</v>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>32932735150</v>
+        <v>158425202980</v>
       </c>
       <c r="P14" t="n">
-        <v>10360</v>
+        <v>30550</v>
       </c>
       <c r="Q14" t="n">
-        <v>2965</v>
+        <v>6100</v>
       </c>
       <c r="R14" t="n">
-        <v>61000</v>
+        <v>149000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>미국 양자 보안주 폭등 및 세계 최초 기술 관련 긍정적 언급. 그러나 단기 과열 및 프로그램 매도세 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['양자 보안', '세계 최초', '단기 과열']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G15" t="n">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="H15" t="n">
         <v>50.27</v>
@@ -1806,7 +1806,7 @@
         <v>50.47</v>
       </c>
       <c r="O15" t="n">
-        <v>2425452655500</v>
+        <v>2473044552000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 관련 긍정적 전망 속 기관 매수세 유입. 금리 인상 및 시장 변동성 주의.</t>
+          <t>나스닥 선물 흐름 및 AI 관련 긍정적 전망. 그러나 외인 매도세 및 주가 변동성 관찰.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '기관', '시장']</t>
+          <t>['AI', '나스닥', '외인 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10070</v>
+        <v>14770</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>139</v>
+      </c>
+      <c r="F16" t="n">
+        <v>81</v>
+      </c>
+      <c r="G16" t="n">
+        <v>316</v>
+      </c>
+      <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>86</v>
-      </c>
-      <c r="F16" t="n">
-        <v>43</v>
-      </c>
-      <c r="G16" t="n">
-        <v>94</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.6</v>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9990</v>
+        <v>14660</v>
       </c>
       <c r="K16" t="n">
-        <v>10110</v>
+        <v>14980</v>
       </c>
       <c r="L16" t="n">
-        <v>11390</v>
+        <v>15460</v>
       </c>
       <c r="M16" t="n">
-        <v>9980</v>
+        <v>14330</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6</v>
+        <v>1.17</v>
       </c>
       <c r="O16" t="n">
-        <v>146800373925</v>
+        <v>40182474470</v>
       </c>
       <c r="P16" t="n">
-        <v>15960</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>3500</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>21000</v>
+        <v>-7000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 부정적 언급 다수. 신약 관련 기대감 있으나 구체적 근거 부족.</t>
+          <t>국제 유가 상승에도 주가 약보합세. 이란 관련 지정학적 리스크 및 수급 불안정.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '신약']</t>
+          <t>['국제유가', '지정학적리스크', '수급불안정']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G17" t="n">
         <v>1706</v>
@@ -1990,7 +1990,7 @@
         <v>46.64</v>
       </c>
       <c r="O17" t="n">
-        <v>1311345993500</v>
+        <v>1353015602750</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>시장 안정화 기대감 속 저가 매수 기회 언급. 일부 악재 선반영 및 반등 가능성 전망.</t>
+          <t>시장 안정화 및 저가 매수 기회 언급. 악재 선반영 후 반등 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['시장', '반등', '저가매수']</t>
+          <t>['시장 안정화', '저가 매수', '반등']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,83 +2035,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14730</v>
+        <v>226000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.17</v>
+        <v>0.15</v>
       </c>
       <c r="E18" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F18" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G18" t="n">
-        <v>314</v>
+        <v>769</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14660</v>
+        <v>225000</v>
       </c>
       <c r="K18" t="n">
-        <v>14980</v>
+        <v>228500</v>
       </c>
       <c r="L18" t="n">
-        <v>15460</v>
+        <v>229000</v>
       </c>
       <c r="M18" t="n">
-        <v>14330</v>
+        <v>219500</v>
       </c>
       <c r="N18" t="n">
-        <v>1.17</v>
+        <v>7.05</v>
       </c>
       <c r="O18" t="n">
-        <v>39843514150</v>
+        <v>71808915750</v>
       </c>
       <c r="P18" t="n">
-        <v>36200</v>
+        <v>426000</v>
       </c>
       <c r="Q18" t="n">
-        <v>8920</v>
+        <v>89500</v>
       </c>
       <c r="R18" t="n">
-        <v>-7000</v>
+        <v>-110000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>국제 유가 상승에도 주가 약보합세. 이란 관련 지정학적 리스크 및 수급 불안정.</t>
+          <t>테슬라 테라팹 공급 계약 체결. AI 반도체 시장 성장 및 주주 환원 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적리스크', '수급불안정']</t>
+          <t>['테슬라', '테라팹', 'AI반도체']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>226000</v>
+        <v>10020</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>759</v>
+        <v>98</v>
       </c>
       <c r="H19" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>225000</v>
+        <v>9990</v>
       </c>
       <c r="K19" t="n">
-        <v>228500</v>
+        <v>10110</v>
       </c>
       <c r="L19" t="n">
-        <v>229000</v>
+        <v>11390</v>
       </c>
       <c r="M19" t="n">
-        <v>219500</v>
+        <v>9980</v>
       </c>
       <c r="N19" t="n">
-        <v>7.05</v>
+        <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>71262225000</v>
+        <v>147198512625</v>
       </c>
       <c r="P19" t="n">
-        <v>426000</v>
+        <v>15960</v>
       </c>
       <c r="Q19" t="n">
-        <v>89500</v>
+        <v>3500</v>
       </c>
       <c r="R19" t="n">
-        <v>-110000</v>
+        <v>21000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>테슬라 테라팹 공급 계약 체결. AI 반도체 시장 성장 및 주주 환원 기대.</t>
+          <t>주가 조작 및 공매도 관련 부정적 언급 다수. 신약 개발 기대감 있으나 불확실.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['테슬라', '테라팹', 'AI반도체']</t>
+          <t>['주가 조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14390</v>
+        <v>14370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.69%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F20" t="n">
         <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H20" t="n">
         <v>1.8</v>
@@ -2266,7 +2266,7 @@
         <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>48752084765</v>
+        <v>49372388825</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>광통신 관련주 동반 상승 속 주가 키 맞추기 기대. 외국인 보유율 안정적.</t>
+          <t>방송 홍보 내용 언급과 함께 주가 회복 및 상승에 대한 기대감이 나타남. 특정 가격 목표치 제시 및 외국인 보유율 관련 긍정적 요인이 부각됨.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '키맞추기', '외국인']</t>
+          <t>['광통신', 'AI', 'FOMC']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86200</v>
+        <v>8760</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="F21" t="n">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>711</v>
+        <v>337</v>
       </c>
       <c r="H21" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K21" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L21" t="n">
-        <v>86800</v>
+        <v>8840</v>
       </c>
       <c r="M21" t="n">
-        <v>85000</v>
+        <v>8670</v>
       </c>
       <c r="N21" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O21" t="n">
-        <v>88374096900</v>
+        <v>16227222325</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R21" t="n">
-        <v>-169000</v>
+        <v>-290000</v>
       </c>
       <c r="S21" t="n">
-        <v>-55000</v>
+        <v>-1000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 사업 확대 기대감 속 긍정적 전망. 유가 상승 및 에너지 독립 필요성 부각.</t>
+          <t>글로벌 디스플레이 업체 대비 저평가 주장. 그러나 적자 지속 및 목표주가 하향으로 인한 부정적 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '에너지', '유가']</t>
+          <t>['저평가', '적자', '목표주가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8760</v>
+        <v>86000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.02%</t>
+          <t>'-1.15%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="G22" t="n">
-        <v>328</v>
+        <v>722</v>
       </c>
       <c r="H22" t="n">
-        <v>27.16</v>
+        <v>23.45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>8850</v>
+        <v>87000</v>
       </c>
       <c r="K22" t="n">
-        <v>8750</v>
+        <v>86200</v>
       </c>
       <c r="L22" t="n">
-        <v>8840</v>
+        <v>86800</v>
       </c>
       <c r="M22" t="n">
-        <v>8670</v>
+        <v>85000</v>
       </c>
       <c r="N22" t="n">
-        <v>27.16</v>
+        <v>23.56</v>
       </c>
       <c r="O22" t="n">
-        <v>15901830565</v>
+        <v>89299750650</v>
       </c>
       <c r="P22" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q22" t="n">
-        <v>8120</v>
+        <v>57000</v>
       </c>
       <c r="R22" t="n">
-        <v>-290000</v>
+        <v>-169000</v>
       </c>
       <c r="S22" t="n">
-        <v>-1000</v>
+        <v>-55000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>경영진 교체 요구 및 실적 부진 지속. 목표주가 하향 조정 및 저평가 논란.</t>
+          <t>원전 사업 확대 기대감 속 긍정적 전망. 유가 상승 및 에너지 독립 필요성 부각.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['실적', '목표주가', '경영진']</t>
+          <t>['원전', '에너지', '유가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4180</v>
+        <v>4190</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.35%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H23" t="n">
         <v>0.77</v>
@@ -2542,7 +2542,7 @@
         <v>0.59</v>
       </c>
       <c r="O23" t="n">
-        <v>63241928581</v>
+        <v>63925339722</v>
       </c>
       <c r="P23" t="n">
         <v>8100</v>
@@ -2602,13 +2602,13 @@
         <v>0.09</v>
       </c>
       <c r="E24" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F24" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G24" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H24" t="n">
         <v>28.9</v>
@@ -2634,7 +2634,7 @@
         <v>28.81</v>
       </c>
       <c r="O24" t="n">
-        <v>49266479275</v>
+        <v>49839242225</v>
       </c>
       <c r="P24" t="n">
         <v>35350</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 주가 하락. 조선업 전망 및 자사주 소각 등 추가 조치 요구.</t>
+          <t>12억 달러 수주 공시로 인한 상승 기대 있으나, 낮은 상승률과 매도세로 인한 실망감.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['수주공시', '조선업', '자사주소각']</t>
+          <t>['수주 공시', '조선주', '매도세']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260915_12.xlsx
+++ b/data/trending_integrated_20260915_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3000</v>
+        <v>3005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.05%</t>
+          <t>'+16.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>73557376240</v>
+        <v>76322231711</v>
       </c>
       <c r="P2" t="n">
         <v>5100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 기업과 594억 공급 계약 및 세계 최초 타이틀. 트럼프 AI 발언에 따른 기대감 상승.</t>
+          <t>삼성과 4381억 계약 체결 및 세계 최초 타이틀 기반 급등 전망. 거래량 및 프로그램 매매 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공급 계약', 'AI', '세계 최초']</t>
+          <t>['계약체결', '세계최초', '프로그램']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10680</v>
+        <v>10720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.21%</t>
+          <t>'+15.64%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H3" t="n">
         <v>1.19</v>
@@ -702,7 +702,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>136043486895</v>
+        <v>136606557945</v>
       </c>
       <c r="P3" t="n">
         <v>25050</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25000</v>
+        <v>25100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.16%</t>
+          <t>'+14.61%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -794,7 +794,7 @@
         <v>4.89</v>
       </c>
       <c r="O4" t="n">
-        <v>187306207875</v>
+        <v>188854190175</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51200</v>
+        <v>35500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.11%</t>
+          <t>'+7.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.18</v>
+        <v>-0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>424</v>
+        <v>261</v>
       </c>
       <c r="H5" t="n">
-        <v>13.97</v>
+        <v>14.93</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>47800</v>
+        <v>33000</v>
       </c>
       <c r="K5" t="n">
-        <v>47300</v>
+        <v>32750</v>
       </c>
       <c r="L5" t="n">
-        <v>54600</v>
+        <v>37200</v>
       </c>
       <c r="M5" t="n">
-        <v>46400</v>
+        <v>32750</v>
       </c>
       <c r="N5" t="n">
-        <v>14.15</v>
+        <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>76108666075</v>
+        <v>44839487725</v>
       </c>
       <c r="P5" t="n">
-        <v>108900</v>
+        <v>50400</v>
       </c>
       <c r="Q5" t="n">
-        <v>18230</v>
+        <v>23650</v>
       </c>
       <c r="R5" t="n">
-        <v>89000</v>
+        <v>318000</v>
       </c>
       <c r="S5" t="n">
-        <v>21000</v>
+        <v>73000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>연이은 대형 수주 공시 기반으로 한 긍정적 전망. 수소법 시행 및 시장 확대 기대.</t>
+          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['수주 공시', '수소법', '대형 계약']</t>
+          <t>['저PBR', '현대제철', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,82 +919,82 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35250</v>
+        <v>3630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.82%</t>
+          <t>'+6.76%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>270</v>
+        <v>179</v>
       </c>
       <c r="H6" t="n">
-        <v>14.93</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33000</v>
+        <v>3400</v>
       </c>
       <c r="K6" t="n">
-        <v>32750</v>
+        <v>3450</v>
       </c>
       <c r="L6" t="n">
-        <v>37200</v>
+        <v>4080</v>
       </c>
       <c r="M6" t="n">
-        <v>32750</v>
+        <v>3445</v>
       </c>
       <c r="N6" t="n">
-        <v>15.06</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>43885139825</v>
+        <v>141473222538</v>
       </c>
       <c r="P6" t="n">
-        <v>50400</v>
+        <v>4335</v>
       </c>
       <c r="Q6" t="n">
-        <v>23650</v>
+        <v>1246</v>
       </c>
       <c r="R6" t="n">
-        <v>318000</v>
+        <v>226000</v>
       </c>
       <c r="S6" t="n">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
+          <t>삼익제약과의 경쟁 구도 속에서 주가 변동성. 단기 트레이딩 관점 및 3700원 돌파 여부 주목.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저PBR', '현대제철', '상승']</t>
+          <t>['단타', '삼익제약', '3700원']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,99 +1016,99 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3620</v>
+        <v>50800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.47%</t>
+          <t>'+6.28%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>178</v>
+        <v>446</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>13.97</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3400</v>
+        <v>47800</v>
       </c>
       <c r="K7" t="n">
-        <v>3450</v>
+        <v>47300</v>
       </c>
       <c r="L7" t="n">
-        <v>4080</v>
+        <v>54600</v>
       </c>
       <c r="M7" t="n">
-        <v>3445</v>
+        <v>46400</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>14.15</v>
       </c>
       <c r="O7" t="n">
-        <v>141088224242</v>
+        <v>76852281975</v>
       </c>
       <c r="P7" t="n">
-        <v>4335</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1246</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>226000</v>
+        <v>89000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼익제약과의 경쟁 구도 속에서 주가 변동성. 단기 트레이딩 관점 및 3700원 돌파 여부 주목.</t>
+          <t>연이은 수주 공시 기반으로 주가 상승 기대. 외인, 보험, 투신, 연기금 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단타', '삼익제약', '3700원']</t>
+          <t>['수주', '공시', '수소법']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31950</v>
+        <v>32000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.27%</t>
+          <t>'+5.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G8" t="n">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="H8" t="n">
         <v>17.5</v>
@@ -1162,7 +1162,7 @@
         <v>17.55</v>
       </c>
       <c r="O8" t="n">
-        <v>11288019275</v>
+        <v>11479590700</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14830</v>
+        <v>14820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.10%</t>
+          <t>'+5.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H9" t="n">
         <v>10.75</v>
@@ -1254,7 +1254,7 @@
         <v>10.69</v>
       </c>
       <c r="O9" t="n">
-        <v>106838262475</v>
+        <v>107934984205</v>
       </c>
       <c r="P9" t="n">
         <v>23550</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142000</v>
+        <v>142400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.88%</t>
+          <t>'+4.17%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H10" t="n">
         <v>15.81</v>
@@ -1346,7 +1346,7 @@
         <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>93580324050</v>
+        <v>94575441100</v>
       </c>
       <c r="P10" t="n">
         <v>164700</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>합병 반대 주장과 함께 주가 하락 및 폭락에 대한 우려가 제기됨. 일부 긍정적 요인 언급에도 불구하고 부정적 전망이 우세함.</t>
+          <t>합병 반대 의견 및 정정신고서 미제출 시 합병 철회 가능성 언급. 주가 하락 및 흔들림에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['합병', '정정신고서', '폭락']</t>
+          <t>['합병', '주주총회', '정정신고서']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,79 +1391,79 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7140</v>
+        <v>10550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.48%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.97</v>
+        <v>0.26</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>401</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7</v>
+        <v>17.93</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6900</v>
+        <v>10270</v>
       </c>
       <c r="K11" t="n">
-        <v>7500</v>
+        <v>11000</v>
       </c>
       <c r="L11" t="n">
-        <v>8190</v>
+        <v>11650</v>
       </c>
       <c r="M11" t="n">
-        <v>6730</v>
+        <v>10010</v>
       </c>
       <c r="N11" t="n">
-        <v>1.67</v>
+        <v>17.67</v>
       </c>
       <c r="O11" t="n">
-        <v>37226223145</v>
+        <v>320116995055</v>
       </c>
       <c r="P11" t="n">
-        <v>10360</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>2965</v>
+        <v>1760</v>
       </c>
       <c r="R11" t="n">
-        <v>61000</v>
+        <v>276000</v>
       </c>
       <c r="S11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>광통신 대장주로서 아이온큐 급등과 연계한 상승 기대감. 트럼프 AI 정책 수혜 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['광통신', 'AI', '아이온큐']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10540</v>
+        <v>19150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.63%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.26</v>
+        <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>394</v>
+        <v>319</v>
       </c>
       <c r="H12" t="n">
-        <v>17.93</v>
+        <v>10.53</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,130 +1515,130 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10270</v>
+        <v>18760</v>
       </c>
       <c r="K12" t="n">
-        <v>11000</v>
+        <v>18440</v>
       </c>
       <c r="L12" t="n">
-        <v>11650</v>
+        <v>19330</v>
       </c>
       <c r="M12" t="n">
-        <v>10010</v>
+        <v>18120</v>
       </c>
       <c r="N12" t="n">
-        <v>17.67</v>
+        <v>10.55</v>
       </c>
       <c r="O12" t="n">
-        <v>318860712795</v>
+        <v>52568198245</v>
       </c>
       <c r="P12" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1760</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>276000</v>
+        <v>-67000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 발전 기대감 및 아이온큐 급등에 따른 긍정적 전망. 그러나 객관적 근거 부족.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '아이온큐', '광통신']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19220</v>
+        <v>7020</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.45%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>-0.97</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>311</v>
+        <v>118</v>
       </c>
       <c r="H13" t="n">
-        <v>10.53</v>
+        <v>0.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18760</v>
+        <v>6900</v>
       </c>
       <c r="K13" t="n">
-        <v>18440</v>
+        <v>7500</v>
       </c>
       <c r="L13" t="n">
-        <v>19330</v>
+        <v>8190</v>
       </c>
       <c r="M13" t="n">
-        <v>18120</v>
+        <v>6730</v>
       </c>
       <c r="N13" t="n">
-        <v>10.55</v>
+        <v>1.67</v>
       </c>
       <c r="O13" t="n">
-        <v>51295027705</v>
+        <v>41289844030</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>10360</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>2965</v>
       </c>
       <c r="R13" t="n">
-        <v>-67000</v>
+        <v>61000</v>
       </c>
       <c r="S13" t="n">
-        <v>-18000</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17530</v>
+        <v>17450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.92%</t>
+          <t>'+1.45%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-2.35</v>
       </c>
       <c r="E14" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H14" t="n">
         <v>0.35</v>
@@ -1714,7 +1714,7 @@
         <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>158425202980</v>
+        <v>161733797510</v>
       </c>
       <c r="P14" t="n">
         <v>30550</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등 및 세계 최초 기술 관련 긍정적 언급. 그러나 단기 과열 및 프로그램 매도세 관찰.</t>
+          <t>양자 보안주로 분류되며 신고가 경신. 미국 보안주 폭등 및 세계 최초 타이틀 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자 보안', '세계 최초', '단기 과열']</t>
+          <t>['양자보안', '신고가', '미국보안주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G15" t="n">
-        <v>2115</v>
+        <v>2084</v>
       </c>
       <c r="H15" t="n">
         <v>50.27</v>
@@ -1806,7 +1806,7 @@
         <v>50.47</v>
       </c>
       <c r="O15" t="n">
-        <v>2473044552000</v>
+        <v>2532468004000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14770</v>
+        <v>14780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.75%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-1.17</v>
       </c>
       <c r="E16" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F16" t="n">
         <v>81</v>
       </c>
       <c r="G16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>1.17</v>
       </c>
       <c r="O16" t="n">
-        <v>40182474470</v>
+        <v>40584307600</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G17" t="n">
-        <v>1706</v>
+        <v>1711</v>
       </c>
       <c r="H17" t="n">
         <v>46.57</v>
@@ -1990,7 +1990,7 @@
         <v>46.64</v>
       </c>
       <c r="O17" t="n">
-        <v>1353015602750</v>
+        <v>1392051571000</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>226000</v>
+        <v>225500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="n">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="H18" t="n">
         <v>7.2</v>
@@ -2082,7 +2082,7 @@
         <v>7.05</v>
       </c>
       <c r="O18" t="n">
-        <v>71808915750</v>
+        <v>72410996500</v>
       </c>
       <c r="P18" t="n">
         <v>426000</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>테슬라 테라팹 공급 계약 체결. AI 반도체 시장 성장 및 주주 환원 기대.</t>
+          <t>머스크 테슬라 '테라팹' 공급 계약 소식 기반 급등 기대. 공매도 세력 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['테슬라', '테라팹', 'AI반도체']</t>
+          <t>['테라팹', '공급', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10020</v>
+        <v>10010</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
         <v>43</v>
@@ -2174,7 +2174,7 @@
         <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>147198512625</v>
+        <v>147519562905</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2234,13 +2234,13 @@
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
         <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="H20" t="n">
         <v>1.8</v>
@@ -2266,7 +2266,7 @@
         <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>49372388825</v>
+        <v>50083877850</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>방송 홍보 내용 언급과 함께 주가 회복 및 상승에 대한 기대감이 나타남. 특정 가격 목표치 제시 및 외국인 보유율 관련 긍정적 요인이 부각됨.</t>
+          <t>머니투데이 방송 홍보 및 광전자 대비 상대적 상승 기대감. 외국인 보유율 바닥 및 지지선 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', 'FOMC']</t>
+          <t>['광통신', '홍보', '외국인보유율']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8760</v>
+        <v>8750</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.02%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
         <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="H21" t="n">
         <v>27.16</v>
@@ -2358,7 +2358,7 @@
         <v>27.16</v>
       </c>
       <c r="O21" t="n">
-        <v>16227222325</v>
+        <v>16319133505</v>
       </c>
       <c r="P21" t="n">
         <v>17950</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>글로벌 디스플레이 업체 대비 저평가 주장. 그러나 적자 지속 및 목표주가 하향으로 인한 부정적 전망.</t>
+          <t>하반기 목표주가 11000원 제시 및 PBR 기반 저평가 주장. 그러나 적자 및 ADR 폭락 등 부정적 요인 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['저평가', '적자', '목표주가']</t>
+          <t>['목표주가', 'PBR', 'ADR']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86000</v>
+        <v>85800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.15%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F22" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="H22" t="n">
         <v>23.45</v>
@@ -2450,7 +2450,7 @@
         <v>23.56</v>
       </c>
       <c r="O22" t="n">
-        <v>89299750650</v>
+        <v>91066924550</v>
       </c>
       <c r="P22" t="n">
         <v>139200</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4190</v>
+        <v>4170</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-3.58%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.18</v>
       </c>
       <c r="E23" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H23" t="n">
         <v>0.77</v>
@@ -2542,7 +2542,7 @@
         <v>0.59</v>
       </c>
       <c r="O23" t="n">
-        <v>63925339722</v>
+        <v>64593852239</v>
       </c>
       <c r="P23" t="n">
         <v>8100</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21050</v>
+        <v>21000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-4.98%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.09</v>
       </c>
       <c r="E24" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F24" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G24" t="n">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="H24" t="n">
         <v>28.9</v>
@@ -2628,13 +2628,13 @@
         <v>21850</v>
       </c>
       <c r="M24" t="n">
-        <v>20950</v>
+        <v>20900</v>
       </c>
       <c r="N24" t="n">
         <v>28.81</v>
       </c>
       <c r="O24" t="n">
-        <v>49839242225</v>
+        <v>52640358175</v>
       </c>
       <c r="P24" t="n">
         <v>35350</v>

--- a/data/trending_integrated_20260915_12.xlsx
+++ b/data/trending_integrated_20260915_12.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3005</v>
+        <v>10760</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.25%</t>
+          <t>'+16.07%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.34</v>
+        <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G2" t="n">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="H2" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2585</v>
+        <v>9270</v>
       </c>
       <c r="K2" t="n">
-        <v>2725</v>
+        <v>9810</v>
       </c>
       <c r="L2" t="n">
-        <v>3200</v>
+        <v>12050</v>
       </c>
       <c r="M2" t="n">
-        <v>2690</v>
+        <v>9800</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>76322231711</v>
+        <v>137132624050</v>
       </c>
       <c r="P2" t="n">
-        <v>5100</v>
+        <v>25050</v>
       </c>
       <c r="Q2" t="n">
-        <v>966</v>
+        <v>3705</v>
       </c>
       <c r="R2" t="n">
-        <v>-461000</v>
+        <v>16000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성과 4381억 계약 체결 및 세계 최초 타이틀 기반 급등 전망. 거래량 및 프로그램 매매 언급.</t>
+          <t>노보노디스크와의 협력 및 장기 지속형 주사제 개발 기대감. 품절주 특징 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['계약체결', '세계최초', '프로그램']</t>
+          <t>['장기지속형주사제', '품절주', '노보노디스크']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10720</v>
+        <v>2990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.64%</t>
+          <t>'+15.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.06</v>
+        <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="H3" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9270</v>
+        <v>2585</v>
       </c>
       <c r="K3" t="n">
-        <v>9810</v>
+        <v>2725</v>
       </c>
       <c r="L3" t="n">
-        <v>12050</v>
+        <v>3200</v>
       </c>
       <c r="M3" t="n">
-        <v>9800</v>
+        <v>2690</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>136606557945</v>
+        <v>77525344979</v>
       </c>
       <c r="P3" t="n">
-        <v>25050</v>
+        <v>5100</v>
       </c>
       <c r="Q3" t="n">
-        <v>3705</v>
+        <v>966</v>
       </c>
       <c r="R3" t="n">
-        <v>16000</v>
+        <v>-461000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>품절주 특성 및 장기지속형 주사제 관련 기대감으로 인한 강한 상승세.</t>
+          <t>삼성과의 4381억 계약 체결 완료. 세계 최초 기술 및 AI 발전 관련 긍정적 뉴스에 따른 급등 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['품절주', '장기지속형 주사제', '상승세']</t>
+          <t>['계약', 'AI', '세계최초']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25100</v>
+        <v>24950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.61%</t>
+          <t>'+13.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -794,7 +794,7 @@
         <v>4.89</v>
       </c>
       <c r="O4" t="n">
-        <v>188854190175</v>
+        <v>189869713150</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35500</v>
+        <v>35350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.58%</t>
+          <t>'+7.12%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H5" t="n">
         <v>14.93</v>
@@ -886,7 +886,7 @@
         <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>44839487725</v>
+        <v>45100035125</v>
       </c>
       <c r="P5" t="n">
         <v>50400</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3630</v>
+        <v>3640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.76%</t>
+          <t>'+7.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H6" t="n">
         <v>0.83</v>
@@ -978,7 +978,7 @@
         <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>141473222538</v>
+        <v>141857351131</v>
       </c>
       <c r="P6" t="n">
         <v>4335</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50800</v>
+        <v>51100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.28%</t>
+          <t>'+6.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
         <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="H7" t="n">
         <v>13.97</v>
@@ -1070,7 +1070,7 @@
         <v>14.15</v>
       </c>
       <c r="O7" t="n">
-        <v>76852281975</v>
+        <v>77450089125</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>연이은 수주 공시 기반으로 주가 상승 기대. 외인, 보험, 투신, 연기금 매수세 유입 확인.</t>
+          <t>연이은 수주 공시에도 주가 반응 미미. 공매도 세력과의 공방 및 향후 수주 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '공시', '수소법']</t>
+          <t>['수주', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,79 +1115,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32000</v>
+        <v>14870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.44%</t>
+          <t>'+5.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>148</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>776</v>
+        <v>167</v>
       </c>
       <c r="H8" t="n">
-        <v>17.5</v>
+        <v>10.75</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>30350</v>
+        <v>14110</v>
       </c>
       <c r="K8" t="n">
-        <v>30250</v>
+        <v>14110</v>
       </c>
       <c r="L8" t="n">
-        <v>32300</v>
+        <v>15250</v>
       </c>
       <c r="M8" t="n">
-        <v>30250</v>
+        <v>13400</v>
       </c>
       <c r="N8" t="n">
-        <v>17.55</v>
+        <v>10.69</v>
       </c>
       <c r="O8" t="n">
-        <v>11479590700</v>
+        <v>108582930025</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>23550</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>5700</v>
       </c>
       <c r="R8" t="n">
-        <v>25000</v>
+        <v>-68000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 관련 기대감과 동시에 실패 가능성 및 유증 관련 부정적 언급.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA 승인', '유증']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,91 +1195,91 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14820</v>
+        <v>31950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.03%</t>
+          <t>'+5.27%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="G9" t="n">
-        <v>164</v>
+        <v>790</v>
       </c>
       <c r="H9" t="n">
-        <v>10.75</v>
+        <v>17.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14110</v>
+        <v>30350</v>
       </c>
       <c r="K9" t="n">
-        <v>14110</v>
+        <v>30250</v>
       </c>
       <c r="L9" t="n">
-        <v>15250</v>
+        <v>32300</v>
       </c>
       <c r="M9" t="n">
-        <v>13400</v>
+        <v>30250</v>
       </c>
       <c r="N9" t="n">
-        <v>10.69</v>
+        <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>107934984205</v>
+        <v>11587320675</v>
       </c>
       <c r="P9" t="n">
-        <v>23550</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>5700</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-68000</v>
+        <v>25000</v>
       </c>
       <c r="S9" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>담관암 FDA 승인 결과 발표 임박 및 유증 이슈. 승인 기대감과 함께 부정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['담관암', 'FDA', '유증']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142400</v>
+        <v>142600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.17%</t>
+          <t>'+4.32%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="H10" t="n">
         <v>15.81</v>
@@ -1346,7 +1346,7 @@
         <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>94575441100</v>
+        <v>95736588900</v>
       </c>
       <c r="P10" t="n">
         <v>164700</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>합병 반대 의견 및 정정신고서 미제출 시 합병 철회 가능성 언급. 주가 하락 및 흔들림에 대한 불만 표출.</t>
+          <t>합병 반대 촉구와 함께 주가 하락 및 흔들림에 대한 우려 제기. 부정적인 전망과 함께 단기 시세 조작 의혹 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['합병', '주주총회', '정정신고서']</t>
+          <t>['합병', '정정신고서', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10550</v>
+        <v>10510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.34%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.26</v>
       </c>
       <c r="E11" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F11" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G11" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H11" t="n">
         <v>17.93</v>
@@ -1438,7 +1438,7 @@
         <v>17.67</v>
       </c>
       <c r="O11" t="n">
-        <v>320116995055</v>
+        <v>321338084375</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1498,13 +1498,13 @@
         <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H12" t="n">
         <v>10.53</v>
@@ -1530,7 +1530,7 @@
         <v>10.55</v>
       </c>
       <c r="O12" t="n">
-        <v>52568198245</v>
+        <v>53869877885</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7020</v>
+        <v>17530</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+1.92%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.97</v>
+        <v>-2.35</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="G13" t="n">
-        <v>118</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,143 +1607,143 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6900</v>
+        <v>17200</v>
       </c>
       <c r="K13" t="n">
-        <v>7500</v>
+        <v>17220</v>
       </c>
       <c r="L13" t="n">
-        <v>8190</v>
+        <v>18390</v>
       </c>
       <c r="M13" t="n">
-        <v>6730</v>
+        <v>16600</v>
       </c>
       <c r="N13" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>41289844030</v>
+        <v>163193166150</v>
       </c>
       <c r="P13" t="n">
-        <v>10360</v>
+        <v>30550</v>
       </c>
       <c r="Q13" t="n">
-        <v>2965</v>
+        <v>6100</v>
       </c>
       <c r="R13" t="n">
-        <v>61000</v>
+        <v>149000</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>미국 양자 보안주 강세와 함께 세계 최초 양자 보안 기술 부각. 신고가 경신 및 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['양자보안', '신고가', '세계최초']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17450</v>
+        <v>1714000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.45%</t>
+          <t>'+1.00%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2.35</v>
+        <v>-0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>464</v>
       </c>
       <c r="G14" t="n">
-        <v>229</v>
+        <v>2087</v>
       </c>
       <c r="H14" t="n">
-        <v>0.35</v>
+        <v>50.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17200</v>
+        <v>1697000</v>
       </c>
       <c r="K14" t="n">
-        <v>17220</v>
+        <v>1690000</v>
       </c>
       <c r="L14" t="n">
-        <v>18390</v>
+        <v>1729000</v>
       </c>
       <c r="M14" t="n">
-        <v>16600</v>
+        <v>1685000</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>50.47</v>
       </c>
       <c r="O14" t="n">
-        <v>161733797510</v>
+        <v>2574332173500</v>
       </c>
       <c r="P14" t="n">
-        <v>30550</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>6100</v>
+        <v>325000</v>
       </c>
       <c r="R14" t="n">
-        <v>149000</v>
+        <v>-118000</v>
       </c>
       <c r="S14" t="n">
-        <v>4000</v>
+        <v>-48000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>양자 보안주로 분류되며 신고가 경신. 미국 보안주 폭등 및 세계 최초 타이틀 언급.</t>
+          <t>기관 매수세 유입 및 나스닥 선물 흐름 긍정적. AI 관련 긍정적 전망 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자보안', '신고가', '미국보안주']</t>
+          <t>['기관', 'AI', '나스닥']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1718000</v>
+        <v>14790</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.24%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.2</v>
+        <v>-1.17</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="G15" t="n">
-        <v>2084</v>
+        <v>318</v>
       </c>
       <c r="H15" t="n">
-        <v>50.27</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1697000</v>
+        <v>14660</v>
       </c>
       <c r="K15" t="n">
-        <v>1690000</v>
+        <v>14980</v>
       </c>
       <c r="L15" t="n">
-        <v>1729000</v>
+        <v>15460</v>
       </c>
       <c r="M15" t="n">
-        <v>1685000</v>
+        <v>14330</v>
       </c>
       <c r="N15" t="n">
-        <v>50.47</v>
+        <v>1.17</v>
       </c>
       <c r="O15" t="n">
-        <v>2532468004000</v>
+        <v>40902192540</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>36200</v>
       </c>
       <c r="Q15" t="n">
-        <v>325000</v>
+        <v>8920</v>
       </c>
       <c r="R15" t="n">
-        <v>-118000</v>
+        <v>-7000</v>
       </c>
       <c r="S15" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>나스닥 선물 흐름 및 AI 관련 긍정적 전망. 그러나 외인 매도세 및 주가 변동성 관찰.</t>
+          <t>이란 관련 지정학적 리스크와 유가 변동성 속에서 주가 등락. 외인 수급 변동성 관찰.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '나스닥', '외인 매도']</t>
+          <t>['유가', '지정학적리스크', '외인']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14780</v>
+        <v>6950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+0.72%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.17</v>
+        <v>-0.97</v>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>317</v>
+        <v>124</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14660</v>
+        <v>6900</v>
       </c>
       <c r="K16" t="n">
-        <v>14980</v>
+        <v>7500</v>
       </c>
       <c r="L16" t="n">
-        <v>15460</v>
+        <v>8190</v>
       </c>
       <c r="M16" t="n">
-        <v>14330</v>
+        <v>6730</v>
       </c>
       <c r="N16" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="n">
-        <v>40584307600</v>
+        <v>42225973485</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>10360</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>2965</v>
       </c>
       <c r="R16" t="n">
-        <v>-7000</v>
+        <v>61000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제 유가 상승에도 주가 약보합세. 이란 관련 지정학적 리스크 및 수급 불안정.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적리스크', '수급불안정']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>250750</v>
+        <v>250250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.50%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G17" t="n">
-        <v>1711</v>
+        <v>1723</v>
       </c>
       <c r="H17" t="n">
         <v>46.57</v>
@@ -1990,7 +1990,7 @@
         <v>46.64</v>
       </c>
       <c r="O17" t="n">
-        <v>1392051571000</v>
+        <v>1427715564250</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>225500</v>
+        <v>225750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.15</v>
       </c>
       <c r="E18" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F18" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G18" t="n">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="H18" t="n">
         <v>7.2</v>
@@ -2082,7 +2082,7 @@
         <v>7.05</v>
       </c>
       <c r="O18" t="n">
-        <v>72410996500</v>
+        <v>75400642500</v>
       </c>
       <c r="P18" t="n">
         <v>426000</v>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="H19" t="n">
         <v>0.6</v>
@@ -2174,7 +2174,7 @@
         <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>147519562905</v>
+        <v>147860430845</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 부정적 언급 다수. 신약 개발 기대감 있으나 불확실.</t>
+          <t>주가 조작 의혹 및 공매도 관련 부정적 게시글 다수. 신약 기대감 언급 있으나 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '신약']</t>
+          <t>['주가조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2240,7 +2240,7 @@
         <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="H20" t="n">
         <v>1.8</v>
@@ -2266,7 +2266,7 @@
         <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>50083877850</v>
+        <v>50922480370</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 및 광전자 대비 상대적 상승 기대감. 외국인 보유율 바닥 및 지지선 언급.</t>
+          <t>머니투데이 방송 홍보 언급 및 긍정적 주가 회복 기대. 광통신 섹터 상승 가능성과 외인 보유율 바닥이라는 점 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '홍보', '외국인보유율']</t>
+          <t>['광통신', '머니투데이', '외인보유율']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F21" t="n">
         <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="H21" t="n">
         <v>27.16</v>
@@ -2358,7 +2358,7 @@
         <v>27.16</v>
       </c>
       <c r="O21" t="n">
-        <v>16319133505</v>
+        <v>16576094525</v>
       </c>
       <c r="P21" t="n">
         <v>17950</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>하반기 목표주가 11000원 제시 및 PBR 기반 저평가 주장. 그러나 적자 및 ADR 폭락 등 부정적 요인 언급.</t>
+          <t>대표이사 사퇴 요구 및 목표주가 하향 리포트 언급. 지속적인 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['목표주가', 'PBR', 'ADR']</t>
+          <t>['적자', '목표주가', '리포트']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85800</v>
+        <v>85900</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.26%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="H22" t="n">
         <v>23.45</v>
@@ -2450,7 +2450,7 @@
         <v>23.56</v>
       </c>
       <c r="O22" t="n">
-        <v>91066924550</v>
+        <v>92024945150</v>
       </c>
       <c r="P22" t="n">
         <v>139200</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4170</v>
+        <v>4155</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.58%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.18</v>
       </c>
       <c r="E23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H23" t="n">
         <v>0.77</v>
@@ -2542,7 +2542,7 @@
         <v>0.59</v>
       </c>
       <c r="O23" t="n">
-        <v>64593852239</v>
+        <v>65365011560</v>
       </c>
       <c r="P23" t="n">
         <v>8100</v>
@@ -2602,13 +2602,13 @@
         <v>0.09</v>
       </c>
       <c r="E24" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F24" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G24" t="n">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="H24" t="n">
         <v>28.9</v>
@@ -2634,7 +2634,7 @@
         <v>28.81</v>
       </c>
       <c r="O24" t="n">
-        <v>52640358175</v>
+        <v>53418863250</v>
       </c>
       <c r="P24" t="n">
         <v>35350</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시로 인한 상승 기대 있으나, 낮은 상승률과 매도세로 인한 실망감.</t>
+          <t>12억 달러 수주 공시에도 불구하고 주가 하락에 대한 불만 표출. 수주 실적이 악재로 인식되는 상황.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['수주 공시', '조선주', '매도세']</t>
+          <t>['수주', '공시', '조선']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260915_12.xlsx
+++ b/data/trending_integrated_20260915_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10760</v>
+        <v>10910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.07%</t>
+          <t>'+17.69%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
         <v>1.19</v>
@@ -610,7 +610,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>137132624050</v>
+        <v>144545583070</v>
       </c>
       <c r="P2" t="n">
         <v>25050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2990</v>
+        <v>2995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.67%</t>
+          <t>'+15.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H3" t="n">
         <v>1.34</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>77525344979</v>
+        <v>79395139570</v>
       </c>
       <c r="P3" t="n">
         <v>5100</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성과의 4381억 계약 체결 완료. 세계 최초 기술 및 AI 발전 관련 긍정적 뉴스에 따른 급등 기대.</t>
+          <t>삼성전자 4381억 계약 체결 및 양자/광통신 분야 성장 기대감. 주포 역할 및 반복 단주 거래 의혹 제기.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['계약', 'AI', '세계최초']</t>
+          <t>['양자', '광통신', '계약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24950</v>
+        <v>25250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.93%</t>
+          <t>'+15.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -794,7 +794,7 @@
         <v>4.89</v>
       </c>
       <c r="O4" t="n">
-        <v>189869713150</v>
+        <v>191439603650</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35350</v>
+        <v>35700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.12%</t>
+          <t>'+8.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
         <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H5" t="n">
         <v>14.93</v>
@@ -886,7 +886,7 @@
         <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>45100035125</v>
+        <v>45849320800</v>
       </c>
       <c r="P5" t="n">
         <v>50400</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3640</v>
+        <v>3655</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.06%</t>
+          <t>'+7.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H6" t="n">
         <v>0.83</v>
@@ -978,7 +978,7 @@
         <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>141857351131</v>
+        <v>142737885864</v>
       </c>
       <c r="P6" t="n">
         <v>4335</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51100</v>
+        <v>51000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.90%</t>
+          <t>'+6.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="H7" t="n">
         <v>13.97</v>
@@ -1070,7 +1070,7 @@
         <v>14.15</v>
       </c>
       <c r="O7" t="n">
-        <v>77450089125</v>
+        <v>78145247425</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14870</v>
+        <v>14900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.39%</t>
+          <t>'+5.60%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H8" t="n">
         <v>10.75</v>
@@ -1162,7 +1162,7 @@
         <v>10.69</v>
       </c>
       <c r="O8" t="n">
-        <v>108582930025</v>
+        <v>109223259750</v>
       </c>
       <c r="P8" t="n">
         <v>23550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31950</v>
+        <v>32000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.27%</t>
+          <t>'+5.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="H9" t="n">
         <v>17.5</v>
@@ -1254,7 +1254,7 @@
         <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>11587320675</v>
+        <v>12035804275</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 결과 발표 임박 및 유증 이슈. 승인 기대감과 함께 부정적 전망 혼재.</t>
+          <t>담관암 신약 FDA 승인 관련 기대와 회의론 혼재. 제약 유증 및 CRL 공시 이후 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA', '유증']</t>
+          <t>['담관암', 'FDA', '신약']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142600</v>
+        <v>142900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.32%</t>
+          <t>'+4.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="H10" t="n">
         <v>15.81</v>
@@ -1346,7 +1346,7 @@
         <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>95736588900</v>
+        <v>97136814850</v>
       </c>
       <c r="P10" t="n">
         <v>164700</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>합병 반대 촉구와 함께 주가 하락 및 흔들림에 대한 우려 제기. 부정적인 전망과 함께 단기 시세 조작 의혹 언급.</t>
+          <t>합병 반대 의견 표출 및 우려. 정유/배터리 슈퍼 사이클 기대감과 함께 주가 부양 노력 및 매도세 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['합병', '정정신고서', '주가']</t>
+          <t>['합병', '정유', '배터리']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10510</v>
+        <v>10480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.34%</t>
+          <t>'+2.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.26</v>
       </c>
       <c r="E11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F11" t="n">
         <v>106</v>
       </c>
       <c r="G11" t="n">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="H11" t="n">
         <v>17.93</v>
@@ -1438,7 +1438,7 @@
         <v>17.67</v>
       </c>
       <c r="O11" t="n">
-        <v>321338084375</v>
+        <v>322594338205</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광통신 대장주로서 아이온큐 급등과 연계한 상승 기대감. 트럼프 AI 정책 수혜 가능성 언급.</t>
+          <t>아이온큐 프리마켓 급등 및 트럼프 AI 정책 관련 기대감. 기타법인 매수 유입.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19150</v>
+        <v>19070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+1.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="H12" t="n">
         <v>10.53</v>
@@ -1530,7 +1530,7 @@
         <v>10.55</v>
       </c>
       <c r="O12" t="n">
-        <v>53869877885</v>
+        <v>54699709455</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17530</v>
+        <v>17410</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.92%</t>
+          <t>'+1.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-2.35</v>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F13" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H13" t="n">
         <v>0.35</v>
@@ -1622,7 +1622,7 @@
         <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>163193166150</v>
+        <v>164383068210</v>
       </c>
       <c r="P13" t="n">
         <v>30550</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 강세와 함께 세계 최초 양자 보안 기술 부각. 신고가 경신 및 추가 상승 기대.</t>
+          <t>미국 양자 보안주 폭등에 따른 기대감. '세계최초' 타이틀 중요성 언급. 프로그램 매도세 관찰.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자보안', '신고가', '세계최초']</t>
+          <t>['양자보안', '신고가', '프로그램']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1714000</v>
+        <v>1717000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.00%</t>
+          <t>'+1.18%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="G14" t="n">
-        <v>2087</v>
+        <v>2105</v>
       </c>
       <c r="H14" t="n">
         <v>50.27</v>
@@ -1714,7 +1714,7 @@
         <v>50.47</v>
       </c>
       <c r="O14" t="n">
-        <v>2574332173500</v>
+        <v>2627091075000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기관 매수세 유입 및 나스닥 선물 흐름 긍정적. AI 관련 긍정적 전망 및 주가 상승 기대.</t>
+          <t>나스닥 선물 흐름 및 기관 매수세 유입에 따른 상승 기대감. 트럼프 AI 정책 및 금리 인상 변수 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['기관', 'AI', '나스닥']</t>
+          <t>['AI', '반도체', '기관']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14790</v>
+        <v>14830</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.89%</t>
+          <t>'+1.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.17</v>
       </c>
       <c r="E15" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F15" t="n">
         <v>82</v>
       </c>
       <c r="G15" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>1.17</v>
       </c>
       <c r="O15" t="n">
-        <v>40902192540</v>
+        <v>41248252045</v>
       </c>
       <c r="P15" t="n">
         <v>36200</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크와 유가 변동성 속에서 주가 등락. 외인 수급 변동성 관찰.</t>
+          <t>이란-미국 협상 관련 유가 변동성 언급. 유가 상승 기대감에도 주가 흐름 약보합. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유가', '지정학적리스크', '외인']</t>
+          <t>['유가', '이란', '협상']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,92 +1851,92 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6950</v>
+        <v>10060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.72%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6900</v>
+        <v>9990</v>
       </c>
       <c r="K16" t="n">
-        <v>7500</v>
+        <v>10110</v>
       </c>
       <c r="L16" t="n">
-        <v>8190</v>
+        <v>11390</v>
       </c>
       <c r="M16" t="n">
-        <v>6730</v>
+        <v>9980</v>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>42225973485</v>
+        <v>148559989045</v>
       </c>
       <c r="P16" t="n">
-        <v>10360</v>
+        <v>15960</v>
       </c>
       <c r="Q16" t="n">
-        <v>2965</v>
+        <v>3500</v>
       </c>
       <c r="R16" t="n">
-        <v>61000</v>
+        <v>21000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>주가 조작 의혹 및 공매도 관련 부정적 게시글 다수. 신약 기대감 언급 있으나 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['주가조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>250250</v>
+        <v>250500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.50%</t>
+          <t>'+0.60%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>481</v>
       </c>
       <c r="G17" t="n">
-        <v>1723</v>
+        <v>1706</v>
       </c>
       <c r="H17" t="n">
         <v>46.57</v>
@@ -1990,7 +1990,7 @@
         <v>46.64</v>
       </c>
       <c r="O17" t="n">
-        <v>1427715564250</v>
+        <v>1467828751000</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>시장 안정화 및 저가 매수 기회 언급. 악재 선반영 후 반등 기대.</t>
+          <t>시장 안정화 및 악재 선반영 기대감 속 매수 기회 언급. 노조 이슈 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['시장 안정화', '저가 매수', '반등']</t>
+          <t>['시장', '반도체', '노조']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>225750</v>
+        <v>225500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.15</v>
       </c>
       <c r="E18" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F18" t="n">
         <v>77</v>
       </c>
       <c r="G18" t="n">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H18" t="n">
         <v>7.2</v>
@@ -2082,7 +2082,7 @@
         <v>7.05</v>
       </c>
       <c r="O18" t="n">
-        <v>75400642500</v>
+        <v>75824895250</v>
       </c>
       <c r="P18" t="n">
         <v>426000</v>
@@ -2127,92 +2127,92 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10010</v>
+        <v>6890</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="E19" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>9990</v>
+        <v>6900</v>
       </c>
       <c r="K19" t="n">
-        <v>10110</v>
+        <v>7500</v>
       </c>
       <c r="L19" t="n">
-        <v>11390</v>
+        <v>8190</v>
       </c>
       <c r="M19" t="n">
-        <v>9980</v>
+        <v>6730</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>147860430845</v>
+        <v>43064434950</v>
       </c>
       <c r="P19" t="n">
-        <v>15960</v>
+        <v>10360</v>
       </c>
       <c r="Q19" t="n">
-        <v>3500</v>
+        <v>2965</v>
       </c>
       <c r="R19" t="n">
-        <v>21000</v>
+        <v>61000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 공매도 관련 부정적 게시글 다수. 신약 기대감 언급 있으나 구체적 근거 부족.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '신약']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14370</v>
+        <v>14390</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.69%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F20" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="H20" t="n">
         <v>1.8</v>
@@ -2266,7 +2266,7 @@
         <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>50922480370</v>
+        <v>51278398150</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 언급 및 긍정적 주가 회복 기대. 광통신 섹터 상승 가능성과 외인 보유율 바닥이라는 점 언급.</t>
+          <t>머니투데이 방송 홍보 및 15000원 돌파 기대감. 광전자와의 비교 및 광통신 섹터 전반의 관심.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '머니투데이', '외인보유율']</t>
+          <t>['광통신', '홍보', '15000원']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8750</v>
+        <v>8780</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-0.79%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F21" t="n">
         <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H21" t="n">
         <v>27.16</v>
@@ -2358,7 +2358,7 @@
         <v>27.16</v>
       </c>
       <c r="O21" t="n">
-        <v>16576094525</v>
+        <v>16853383455</v>
       </c>
       <c r="P21" t="n">
         <v>17950</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85900</v>
+        <v>85800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.26%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G22" t="n">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="H22" t="n">
         <v>23.45</v>
@@ -2450,7 +2450,7 @@
         <v>23.56</v>
       </c>
       <c r="O22" t="n">
-        <v>92024945150</v>
+        <v>92808857500</v>
       </c>
       <c r="P22" t="n">
         <v>139200</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4155</v>
+        <v>4180</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.18</v>
       </c>
       <c r="E23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H23" t="n">
         <v>0.77</v>
@@ -2542,7 +2542,7 @@
         <v>0.59</v>
       </c>
       <c r="O23" t="n">
-        <v>65365011560</v>
+        <v>65868047417</v>
       </c>
       <c r="P23" t="n">
         <v>8100</v>
@@ -2602,13 +2602,13 @@
         <v>0.09</v>
       </c>
       <c r="E24" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="F24" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G24" t="n">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="H24" t="n">
         <v>28.9</v>
@@ -2634,7 +2634,7 @@
         <v>28.81</v>
       </c>
       <c r="O24" t="n">
-        <v>53418863250</v>
+        <v>54067089425</v>
       </c>
       <c r="P24" t="n">
         <v>35350</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 불구하고 주가 하락에 대한 불만 표출. 수주 실적이 악재로 인식되는 상황.</t>
+          <t>12억 달러 규모 수주 공시에도 주가 하락. 시장 반응 부정적, 자사주 소각 등 주주환원 정책 요구.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['수주', '공시', '조선']</t>
+          <t>['수주', '조선', '공시']</t>
         </is>
       </c>
       <c r="X24" t="n">
